--- a/Server/Common/GameDatasheet/Original_Item.xlsx
+++ b/Server/Common/GameDatasheet/Original_Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EDDC17-1FAA-459B-AE2F-7FC78771EB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B9EB24-D31D-4498-9E04-7B016251635D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="160">
   <si>
     <t>class_requirement</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>description</t>
-  </si>
-  <si>
-    <t>icon_path</t>
   </si>
   <si>
     <t>quest_item</t>
@@ -84,10 +81,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"Test.png"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sellable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -418,6 +411,136 @@
   </si>
   <si>
     <t>template_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_1.Helmet_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_1.Chest_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_1.Legs_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_1.Gloves_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_1.Boots_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_1.Sword_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_2.Helmet_2"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_2.Chest_2"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_2.Legs_2"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_2.Gloves_2"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_2.Boots_2"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_2.Sword_2"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_3.Helmet_3"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_3.Chest_3"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_3.Legs_3"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_3.Gloves_3"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_3.Boots_3"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_3.Sword_3"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_4.Helmet_4"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_4.Chest_4"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_4.Legs_4"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_4.Gloves_4"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_4.Boots_4"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_4.Sword_4"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_5.Helmet_5"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_5.Chest_5"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_5.Legs_5"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_5.Gloves_5"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_5.Boots_5"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_5.Sword_5"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_6.Helmet_6"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_6.Chest_6"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_6.Legs_6"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_6.Gloves_6"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_6.Boots_6"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_6.Sword_6"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/HpPotion.HpPotion"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/MpPotion.MpPotion"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/MixPotion.MixPotion"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -798,7 +921,7 @@
     <col min="13" max="13" width="10.8984375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.8984375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.69921875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.296875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.69921875" bestFit="1" customWidth="1"/>
@@ -811,22 +934,22 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -853,108 +976,108 @@
         <v>7</v>
       </c>
       <c r="O1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
         <v>10</v>
-      </c>
-      <c r="R1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" t="s">
-        <v>108</v>
-      </c>
-      <c r="T1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" t="s">
-        <v>11</v>
       </c>
       <c r="W1" t="s">
         <v>8</v>
       </c>
       <c r="X1" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="W2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="X2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.4">
@@ -962,13 +1085,13 @@
         <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -977,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -1009,28 +1132,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R3">
         <v>10001</v>
       </c>
       <c r="S3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="X3" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.4">
@@ -1038,13 +1161,13 @@
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
         <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>97</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1053,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1085,28 +1208,28 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R4">
         <v>10001</v>
       </c>
       <c r="S4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="X4" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.4">
@@ -1114,13 +1237,13 @@
         <v>1002</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1129,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1161,28 +1284,28 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R5">
         <v>10001</v>
       </c>
       <c r="S5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X5" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.4">
@@ -1190,13 +1313,13 @@
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -1205,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1237,28 +1360,28 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R6">
         <v>10001</v>
       </c>
       <c r="S6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="X6" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.4">
@@ -1266,13 +1389,13 @@
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1281,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1313,28 +1436,28 @@
         <v>0</v>
       </c>
       <c r="Q7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R7">
         <v>10001</v>
       </c>
       <c r="S7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="X7" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.4">
@@ -1342,13 +1465,13 @@
         <v>1005</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -1357,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1389,28 +1512,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R8">
         <v>10001</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="X8" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.4">
@@ -1418,13 +1541,13 @@
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1433,7 +1556,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1465,28 +1588,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R9">
         <v>10001</v>
       </c>
       <c r="S9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="X9" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.4">
@@ -1494,13 +1617,13 @@
         <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
         <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -1509,7 +1632,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1541,28 +1664,28 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R10">
         <v>10001</v>
       </c>
       <c r="S10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="X10" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.4">
@@ -1570,13 +1693,13 @@
         <v>1008</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1585,7 +1708,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1617,28 +1740,28 @@
         <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R11">
         <v>10001</v>
       </c>
       <c r="S11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="X11" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.4">
@@ -1646,13 +1769,13 @@
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1661,7 +1784,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1693,28 +1816,28 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R12">
         <v>10001</v>
       </c>
       <c r="S12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="X12" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.4">
@@ -1722,13 +1845,13 @@
         <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -1737,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1769,28 +1892,28 @@
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R13">
         <v>10001</v>
       </c>
       <c r="S13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="X13" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.4">
@@ -1798,13 +1921,13 @@
         <v>1011</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1813,7 +1936,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1845,28 +1968,28 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R14">
         <v>10001</v>
       </c>
       <c r="S14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="X14" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.4">
@@ -1874,13 +1997,13 @@
         <v>1012</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1889,7 +2012,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1921,28 +2044,28 @@
         <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R15">
         <v>10001</v>
       </c>
       <c r="S15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X15" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.4">
@@ -1950,13 +2073,13 @@
         <v>1013</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
         <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>97</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1965,7 +2088,7 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1997,28 +2120,28 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R16">
         <v>10001</v>
       </c>
       <c r="S16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="X16" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.4">
@@ -2026,13 +2149,13 @@
         <v>1014</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2041,7 +2164,7 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -2073,28 +2196,28 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R17">
         <v>10001</v>
       </c>
       <c r="S17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="X17" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.4">
@@ -2102,13 +2225,13 @@
         <v>1015</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -2117,7 +2240,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2149,28 +2272,28 @@
         <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R18">
         <v>10001</v>
       </c>
       <c r="S18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="X18" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.4">
@@ -2178,13 +2301,13 @@
         <v>1016</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2193,7 +2316,7 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -2225,28 +2348,28 @@
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R19">
         <v>10001</v>
       </c>
       <c r="S19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="X19" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.4">
@@ -2254,13 +2377,13 @@
         <v>1017</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2269,7 +2392,7 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -2301,28 +2424,28 @@
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R20">
         <v>10001</v>
       </c>
       <c r="S20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="X20" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.4">
@@ -2330,13 +2453,13 @@
         <v>1018</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2345,7 +2468,7 @@
         <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -2377,28 +2500,28 @@
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R21">
         <v>10001</v>
       </c>
       <c r="S21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="X21" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.4">
@@ -2406,13 +2529,13 @@
         <v>1019</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
         <v>95</v>
-      </c>
-      <c r="D22" t="s">
-        <v>97</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -2421,7 +2544,7 @@
         <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -2453,28 +2576,28 @@
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R22">
         <v>10001</v>
       </c>
       <c r="S22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="X22" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.4">
@@ -2482,13 +2605,13 @@
         <v>1020</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -2497,7 +2620,7 @@
         <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -2529,28 +2652,28 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R23">
         <v>10001</v>
       </c>
       <c r="S23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="X23" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.4">
@@ -2558,13 +2681,13 @@
         <v>1021</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -2573,7 +2696,7 @@
         <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2605,28 +2728,28 @@
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R24">
         <v>10001</v>
       </c>
       <c r="S24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="X24" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.4">
@@ -2634,13 +2757,13 @@
         <v>1022</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E25">
         <v>5</v>
@@ -2649,7 +2772,7 @@
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -2681,28 +2804,28 @@
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R25">
         <v>10001</v>
       </c>
       <c r="S25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="X25" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.4">
@@ -2710,13 +2833,13 @@
         <v>1023</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E26">
         <v>6</v>
@@ -2725,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -2757,28 +2880,28 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R26">
         <v>10001</v>
       </c>
       <c r="S26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="X26" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.4">
@@ -2786,13 +2909,13 @@
         <v>1024</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2801,7 +2924,7 @@
         <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -2833,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R27">
         <v>10001</v>
       </c>
       <c r="S27" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T27" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="X27" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.4">
@@ -2862,13 +2985,13 @@
         <v>1025</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s">
         <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>97</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -2877,7 +3000,7 @@
         <v>40</v>
       </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -2909,28 +3032,28 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R28">
         <v>10001</v>
       </c>
       <c r="S28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="X28" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.4">
@@ -2938,13 +3061,13 @@
         <v>1026</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -2953,7 +3076,7 @@
         <v>40</v>
       </c>
       <c r="G29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -2985,28 +3108,28 @@
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R29">
         <v>10001</v>
       </c>
       <c r="S29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="X29" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.4">
@@ -3014,13 +3137,13 @@
         <v>1027</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -3029,7 +3152,7 @@
         <v>40</v>
       </c>
       <c r="G30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -3061,28 +3184,28 @@
         <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R30">
         <v>10001</v>
       </c>
       <c r="S30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X30" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.4">
@@ -3090,13 +3213,13 @@
         <v>1028</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -3105,7 +3228,7 @@
         <v>40</v>
       </c>
       <c r="G31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -3137,28 +3260,28 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R31">
         <v>10001</v>
       </c>
       <c r="S31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U31" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="X31" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.4">
@@ -3166,13 +3289,13 @@
         <v>1029</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -3181,7 +3304,7 @@
         <v>40</v>
       </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -3213,28 +3336,28 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R32">
         <v>10001</v>
       </c>
       <c r="S32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="X32" t="s">
-        <v>17</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.4">
@@ -3242,13 +3365,13 @@
         <v>1030</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -3257,7 +3380,7 @@
         <v>50</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -3289,28 +3412,28 @@
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R33">
         <v>10001</v>
       </c>
       <c r="S33" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T33" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="X33" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.4">
@@ -3318,13 +3441,13 @@
         <v>1031</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" t="s">
         <v>95</v>
-      </c>
-      <c r="D34" t="s">
-        <v>97</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -3333,7 +3456,7 @@
         <v>50</v>
       </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -3365,28 +3488,28 @@
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R34">
         <v>10001</v>
       </c>
       <c r="S34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X34" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.4">
@@ -3394,13 +3517,13 @@
         <v>1032</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -3409,7 +3532,7 @@
         <v>50</v>
       </c>
       <c r="G35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -3441,28 +3564,28 @@
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R35">
         <v>10001</v>
       </c>
       <c r="S35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="X35" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.4">
@@ -3470,13 +3593,13 @@
         <v>1033</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -3485,7 +3608,7 @@
         <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -3517,28 +3640,28 @@
         <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R36">
         <v>10001</v>
       </c>
       <c r="S36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X36" t="s">
-        <v>17</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.4">
@@ -3546,13 +3669,13 @@
         <v>1034</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E37">
         <v>5</v>
@@ -3561,7 +3684,7 @@
         <v>50</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -3593,28 +3716,28 @@
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R37">
         <v>10001</v>
       </c>
       <c r="S37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U37" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="X37" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.4">
@@ -3622,13 +3745,13 @@
         <v>1035</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D38" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E38">
         <v>6</v>
@@ -3637,7 +3760,7 @@
         <v>50</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -3669,28 +3792,28 @@
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R38">
         <v>10001</v>
       </c>
       <c r="S38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="X38" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3731,22 +3854,22 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -3773,108 +3896,108 @@
         <v>7</v>
       </c>
       <c r="O1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
         <v>10</v>
-      </c>
-      <c r="R1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" t="s">
-        <v>108</v>
-      </c>
-      <c r="T1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" t="s">
-        <v>11</v>
       </c>
       <c r="W1" t="s">
         <v>8</v>
       </c>
       <c r="X1" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="W2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="X2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.4">
@@ -3882,22 +4005,22 @@
         <v>2000</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>113</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>115</v>
       </c>
       <c r="H3">
         <v>999</v>
@@ -3928,28 +4051,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R3">
         <v>10001</v>
       </c>
       <c r="S3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="T3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V3">
         <v>10</v>
       </c>
       <c r="W3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="X3" t="s">
-        <v>17</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.4">
@@ -3957,22 +4080,22 @@
         <v>2001</v>
       </c>
       <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
         <v>111</v>
       </c>
-      <c r="C4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>113</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>115</v>
       </c>
       <c r="H4">
         <v>999</v>
@@ -4003,28 +4126,28 @@
         <v>0.3</v>
       </c>
       <c r="Q4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R4">
         <v>10001</v>
       </c>
       <c r="S4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="T4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V4">
         <v>10</v>
       </c>
       <c r="W4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="X4" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.4">
@@ -4032,22 +4155,22 @@
         <v>2002</v>
       </c>
       <c r="B5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" t="s">
         <v>112</v>
       </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
       <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>113</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>115</v>
       </c>
       <c r="H5">
         <v>999</v>
@@ -4078,28 +4201,28 @@
         <v>0.4</v>
       </c>
       <c r="Q5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R5">
         <v>10001</v>
       </c>
       <c r="S5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="T5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V5">
         <v>10</v>
       </c>
       <c r="W5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="X5" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -4118,22 +4241,22 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" t="s">
         <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -4160,108 +4283,108 @@
         <v>7</v>
       </c>
       <c r="O1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
         <v>10</v>
-      </c>
-      <c r="R1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" t="s">
-        <v>108</v>
-      </c>
-      <c r="T1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" t="s">
-        <v>11</v>
       </c>
       <c r="W1" t="s">
         <v>8</v>
       </c>
       <c r="X1" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="O2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="W2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="X2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Server/Common/GameDatasheet/Original_Item.xlsx
+++ b/Server/Common/GameDatasheet/Original_Item.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE28053-EBBB-4FD1-8C4F-EB95BC9B55DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE952D6-72E4-43CC-9C5B-DC9A877363A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="30612" yWindow="-2700" windowWidth="13176" windowHeight="22656" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
-    <sheet name="소비(2000~2999)" sheetId="2" r:id="rId1"/>
-    <sheet name="기타(3000~3999)" sheetId="3" r:id="rId2"/>
+    <sheet name="전사 장비(1000~1999)" sheetId="4" r:id="rId1"/>
+    <sheet name="소비(2000~2999)" sheetId="2" r:id="rId2"/>
+    <sheet name="기타(3000~3999)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="159">
   <si>
     <t>class_requirement</t>
   </si>
@@ -40,30 +41,12 @@
     <t>sell_price</t>
   </si>
   <si>
-    <t>base_attack</t>
-  </si>
-  <si>
-    <t>base_magic_attack</t>
-  </si>
-  <si>
-    <t>hp_bonus</t>
-  </si>
-  <si>
-    <t>mp_bonus</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
-    <t>quest_item</t>
-  </si>
-  <si>
     <t>cooldown</t>
   </si>
   <si>
-    <t>vendor_npc_id</t>
-  </si>
-  <si>
     <t>item_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,10 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>consumable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hp_restore</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,14 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>equippable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>equipment_slot_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"HP 물약"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -169,6 +140,410 @@
   </si>
   <si>
     <t>"/Game/Assets/Icon/MixPotion.MixPotion"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_6.Sword_6"</t>
+  </si>
+  <si>
+    <t>"왕가의 숨겨진 유물 중 하나. 악마와 계약해 얻은 검이라는 소문이 돈다."</t>
+  </si>
+  <si>
+    <t>"TRUE"</t>
+  </si>
+  <si>
+    <t>"warrior"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"sword"</t>
+  </si>
+  <si>
+    <t>"weapon"</t>
+  </si>
+  <si>
+    <t>"저주받은 파멸의 검"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_6.Boots_6"</t>
+  </si>
+  <si>
+    <t>"압도적인 무게감을 가진 신발. 보기만해도 두려워진다."</t>
+  </si>
+  <si>
+    <t>"boots"</t>
+  </si>
+  <si>
+    <t>"armor"</t>
+  </si>
+  <si>
+    <t>"기사 단장의 신발"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_6.Gloves_6"</t>
+  </si>
+  <si>
+    <t>"압도적인 무게감을 가진 건틀릿. 보기만해도 두려워진다."</t>
+  </si>
+  <si>
+    <t>"arms"</t>
+  </si>
+  <si>
+    <t>"기사 단장의 건틀릿"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_6.Legs_6"</t>
+  </si>
+  <si>
+    <t>"압도적인 무게감을 가진 하의. 보기만해도 두려워진다."</t>
+  </si>
+  <si>
+    <t>"legs"</t>
+  </si>
+  <si>
+    <t>"기사 단장의 하의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_6.Chest_6"</t>
+  </si>
+  <si>
+    <t>"압도적인 무게감을 가진 상의. 보기만해도 두려워진다."</t>
+  </si>
+  <si>
+    <t>"chest"</t>
+  </si>
+  <si>
+    <t>"기사 단장의 상의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_6.Helmet_6"</t>
+  </si>
+  <si>
+    <t>"압도적인 무게감을 가진 투구. 보기만해도 두려워진다."</t>
+  </si>
+  <si>
+    <t>"helmet"</t>
+  </si>
+  <si>
+    <t>"기사 단장의 투구"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_5.Sword_5"</t>
+  </si>
+  <si>
+    <t>"보석으로 장식된 화려한 검. 세게 휘두르면 나무도 자를 수 있다."</t>
+  </si>
+  <si>
+    <t>"글라디우스"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_5.Boots_5"</t>
+  </si>
+  <si>
+    <t>"왕실 기사단에 입단할때 수여받는 신발. 품질이 우수한걸로 유명하다."</t>
+  </si>
+  <si>
+    <t>"왕실 기사단의 신발"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_5.Gloves_5"</t>
+  </si>
+  <si>
+    <t>"왕실 기사단에 입단할때 수여받는 건틀릿. 품질이 우수한걸로 유명하다."</t>
+  </si>
+  <si>
+    <t>"왕실 기사단의 건틀릿"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_5.Legs_5"</t>
+  </si>
+  <si>
+    <t>"왕실 기사단에 입단할때 수여받는 하의. 품질이 우수한걸로 유명하다."</t>
+  </si>
+  <si>
+    <t>"왕실 기사단의 하의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_5.Chest_5"</t>
+  </si>
+  <si>
+    <t>"왕실 기사단에 입단할때 수여받는 상의. 품질이 우수한걸로 유명하다."</t>
+  </si>
+  <si>
+    <t>"왕실 기사단의 상의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_5.Helmet_5"</t>
+  </si>
+  <si>
+    <t>"왕실 기사단에 입단할때 수여받는 투구. 품질이 우수한걸로 유명하다."</t>
+  </si>
+  <si>
+    <t>"왕실 기사단의 투구"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_4.Sword_4"</t>
+  </si>
+  <si>
+    <t>"전설로 내려오는 엑스칼리버를 본떠 만든 모조품. 선봉대들 사이에서 인기이다."</t>
+  </si>
+  <si>
+    <t>"엑스칼리버(모조품)"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_4.Boots_4"</t>
+  </si>
+  <si>
+    <t>"선봉대의 신발. 실력있는 기사만이 입을 수 있다."</t>
+  </si>
+  <si>
+    <t>"선봉대의 신발"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_4.Gloves_4"</t>
+  </si>
+  <si>
+    <t>"선봉대의 건틀릿. 실력있는 기사만이 입을 수 있다."</t>
+  </si>
+  <si>
+    <t>"선봉대의 건틀릿"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_4.Legs_4"</t>
+  </si>
+  <si>
+    <t>"선봉대의 하의. 실력있는 기사만이 입을 수 있다."</t>
+  </si>
+  <si>
+    <t>"선봉대의 하의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_4.Chest_4"</t>
+  </si>
+  <si>
+    <t>"선봉대의 상의. 실력있는 기사만이 입을 수 있다."</t>
+  </si>
+  <si>
+    <t>"선봉대의 상의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_4.Helmet_4"</t>
+  </si>
+  <si>
+    <t>"선봉대의 투구. 실력있는 기사만이 입을 수 있다."</t>
+  </si>
+  <si>
+    <t>"선봉대의 투구"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_3.Sword_3"</t>
+  </si>
+  <si>
+    <t>"견습 기사의 A급 검. 사용감이 적어서 그런지 날이 날렵하다."</t>
+  </si>
+  <si>
+    <t>"기사의 검"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_3.Boots_3"</t>
+  </si>
+  <si>
+    <t>"간단한 디자인의 신발. 판금으로 제작되어 꽤 단단하다."</t>
+  </si>
+  <si>
+    <t>"견습 기사의 신발"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_3.Gloves_3"</t>
+  </si>
+  <si>
+    <t>"간단한 디자인의 건틀릿. 판금으로 제작되어 꽤 단단하다."</t>
+  </si>
+  <si>
+    <t>"견습 기사의 건틀릿"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_3.Legs_3"</t>
+  </si>
+  <si>
+    <t>"간단한 디자인의 하의. 판금으로 제작되어 꽤 단단하다."</t>
+  </si>
+  <si>
+    <t>"견습 기사의 하의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_3.Chest_3"</t>
+  </si>
+  <si>
+    <t>"간단한 디자인의 상의. 판금으로 제작되어 꽤 단단하다."</t>
+  </si>
+  <si>
+    <t>"견습 기사의 상의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_3.Helmet_3"</t>
+  </si>
+  <si>
+    <t>"간단한 디자인의 투구. 판금으로 제작되어 꽤 단단하다."</t>
+  </si>
+  <si>
+    <t>"견습 기사의 투구"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_2.Sword_2"</t>
+  </si>
+  <si>
+    <t>"검은날이 매력적인 검. 밤에 휘두르면 잘 보이지 않는다."</t>
+  </si>
+  <si>
+    <t>"흑기사의 검"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_2.Boots_2"</t>
+  </si>
+  <si>
+    <t>"흑기사가 임무를 수행할때 착용하는 신발. 암살용이라 방어력은 그닥 높지 않다."</t>
+  </si>
+  <si>
+    <t>"흑기사의 신발"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_2.Gloves_2"</t>
+  </si>
+  <si>
+    <t>"흑기사가 임무를 수행할때 착용하는 건틀릿. 암살용이라 방어력은 그닥 높지 않다."</t>
+  </si>
+  <si>
+    <t>"흑기사의 건틀릿"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_2.Legs_2"</t>
+  </si>
+  <si>
+    <t>"흑기사가 임무를 수행할때 착용하는 하의. 암살용이라 방어력은 그닥 높지 않다."</t>
+  </si>
+  <si>
+    <t>"흑기사의 하의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_2.Chest_2"</t>
+  </si>
+  <si>
+    <t>"흑기사가 임무를 수행할때 착용하는 상의. 암살용이라 방어력은 그닥 높지 않다."</t>
+  </si>
+  <si>
+    <t>"흑기사의 상의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_2.Helmet_2"</t>
+  </si>
+  <si>
+    <t>"흑기사가 임무를 수행할때 착용하는 복면. 암살용이라 방어력은 그닥 높지 않다."</t>
+  </si>
+  <si>
+    <t>"흑기사의 복면"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Sword_1.Sword_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"날이 빠진 검. 맨손보다 나은 정도다."</t>
+  </si>
+  <si>
+    <t>"FALSE"</t>
+  </si>
+  <si>
+    <t>"초보자의 검"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Boots_1.Boots_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"허름한 신발. 입지 않은 것보다 나은 정도다."</t>
+  </si>
+  <si>
+    <t>"초보자의 신발"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Gloves_1.Gloves_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"허름한 장갑. 입지 않은 것보다 나은 정도다."</t>
+  </si>
+  <si>
+    <t>"초보자의 장갑"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Legs_1.Legs_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"허름한 하의. 입지 않은 것보다 나은 정도다."</t>
+  </si>
+  <si>
+    <t>"초보자의 하의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Chest_1.Chest_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"허름한 상의. 입지 않은 것보다 나은 정도다."</t>
+  </si>
+  <si>
+    <t>"초보자의 상의"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Icon/Helmet_1.Helmet_1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"허름한 두건. 입지 않은 것보다 나은 정도다."</t>
+  </si>
+  <si>
+    <t>"helmet"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"초보자의 두건"</t>
+  </si>
+  <si>
+    <t>asset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_regenerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp_regenerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magical_attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>physical_attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stackable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"FALSE"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -532,8 +907,2475 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E21C8A9-CEC2-4794-9B99-BAC1321823BA}">
+  <dimension ref="A1:U38"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" customWidth="1"/>
+    <col min="5" max="5" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.296875" customWidth="1"/>
+    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" customWidth="1"/>
+    <col min="11" max="11" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="73.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" t="s">
+        <v>156</v>
+      </c>
+      <c r="P1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>154</v>
+      </c>
+      <c r="R1" t="s">
+        <v>153</v>
+      </c>
+      <c r="S1" t="s">
+        <v>152</v>
+      </c>
+      <c r="T1" t="s">
+        <v>151</v>
+      </c>
+      <c r="U1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1000</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H38" si="0">G3*0.1</f>
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>-1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N3" t="s">
+        <v>146</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>100</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R38" si="1">Q3*0.5</f>
+        <v>50</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>1001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>-1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>144</v>
+      </c>
+      <c r="N4" t="s">
+        <v>143</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>200</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>1002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>-1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>141</v>
+      </c>
+      <c r="N5" t="s">
+        <v>140</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>200</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>1003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>158</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>-1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>138</v>
+      </c>
+      <c r="N6" t="s">
+        <v>137</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>1004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>158</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>-1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>135</v>
+      </c>
+      <c r="N7" t="s">
+        <v>134</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>1005</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>-1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N8" t="s">
+        <v>130</v>
+      </c>
+      <c r="O8">
+        <v>10</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>1006</v>
+      </c>
+      <c r="B9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>-1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>200</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>1007</v>
+      </c>
+      <c r="B10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>158</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>-1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>125</v>
+      </c>
+      <c r="N10" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>400</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>1008</v>
+      </c>
+      <c r="B11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11">
+        <v>1000</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>158</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>-1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>122</v>
+      </c>
+      <c r="N11" t="s">
+        <v>121</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>400</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>1009</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>158</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>-1</v>
+      </c>
+      <c r="M12" t="s">
+        <v>119</v>
+      </c>
+      <c r="N12" t="s">
+        <v>118</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>200</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>1010</v>
+      </c>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>158</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>-1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>116</v>
+      </c>
+      <c r="N13" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>200</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>1011</v>
+      </c>
+      <c r="B14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14">
+        <v>2000</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>158</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>-1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>113</v>
+      </c>
+      <c r="N14" t="s">
+        <v>112</v>
+      </c>
+      <c r="O14">
+        <v>35</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>1012</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15">
+        <v>3000</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>-1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>110</v>
+      </c>
+      <c r="N15" t="s">
+        <v>109</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>400</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>1013</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16">
+        <v>3000</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>158</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>-1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" t="s">
+        <v>106</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>800</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>1014</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17">
+        <v>3000</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>158</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>-1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" t="s">
+        <v>103</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>800</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>1015</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18">
+        <v>3000</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>158</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>-1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>101</v>
+      </c>
+      <c r="N18" t="s">
+        <v>100</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>400</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>1016</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19">
+        <v>3000</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>158</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>-1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>98</v>
+      </c>
+      <c r="N19" t="s">
+        <v>97</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>400</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>1017</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20">
+        <v>5000</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>158</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>-1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>95</v>
+      </c>
+      <c r="N20" t="s">
+        <v>94</v>
+      </c>
+      <c r="O20">
+        <v>80</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>1018</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21">
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21">
+        <v>8000</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>158</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>-1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>92</v>
+      </c>
+      <c r="N21" t="s">
+        <v>91</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>800</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>1019</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22">
+        <v>8000</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>158</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>-1</v>
+      </c>
+      <c r="M22" t="s">
+        <v>89</v>
+      </c>
+      <c r="N22" t="s">
+        <v>88</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>1600</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>1020</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23">
+        <v>8000</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>-1</v>
+      </c>
+      <c r="M23" t="s">
+        <v>86</v>
+      </c>
+      <c r="N23" t="s">
+        <v>85</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>1600</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>1021</v>
+      </c>
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24">
+        <v>8000</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>158</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>-1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>83</v>
+      </c>
+      <c r="N24" t="s">
+        <v>82</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>800</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>1022</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25">
+        <v>30</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25">
+        <v>8000</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>158</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>-1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>80</v>
+      </c>
+      <c r="N25" t="s">
+        <v>79</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>800</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>1023</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26">
+        <v>15000</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>158</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>-1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>77</v>
+      </c>
+      <c r="N26" t="s">
+        <v>76</v>
+      </c>
+      <c r="O26">
+        <v>120</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>1024</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27">
+        <v>40</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27">
+        <v>12000</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="I27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" t="s">
+        <v>158</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>-1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>74</v>
+      </c>
+      <c r="N27" t="s">
+        <v>73</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>1600</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>1025</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28">
+        <v>40</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28">
+        <v>12000</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="I28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" t="s">
+        <v>158</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>-1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>71</v>
+      </c>
+      <c r="N28" t="s">
+        <v>70</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3200</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="1"/>
+        <v>1600</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>1026</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29">
+        <v>40</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29">
+        <v>12000</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s">
+        <v>158</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>-1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>68</v>
+      </c>
+      <c r="N29" t="s">
+        <v>67</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>3200</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="1"/>
+        <v>1600</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>1027</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30">
+        <v>40</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30">
+        <v>12000</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="I30" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" t="s">
+        <v>158</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>-1</v>
+      </c>
+      <c r="M30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N30" t="s">
+        <v>64</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>1600</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>1028</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31">
+        <v>40</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31">
+        <v>12000</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="I31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" t="s">
+        <v>158</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>-1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" t="s">
+        <v>61</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>1600</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>1029</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32">
+        <v>40</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32">
+        <v>20000</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="I32" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" t="s">
+        <v>158</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>-1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>59</v>
+      </c>
+      <c r="N32" t="s">
+        <v>58</v>
+      </c>
+      <c r="O32">
+        <v>180</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>1030</v>
+      </c>
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33">
+        <v>50</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33">
+        <v>35000</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="I33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" t="s">
+        <v>158</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" t="s">
+        <v>54</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>4000</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>1031</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34">
+        <v>35000</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="I34" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" t="s">
+        <v>158</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>-1</v>
+      </c>
+      <c r="M34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" t="s">
+        <v>50</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>8000</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>1032</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35">
+        <v>50</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35">
+        <v>35000</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="I35" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" t="s">
+        <v>158</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>-1</v>
+      </c>
+      <c r="M35" t="s">
+        <v>47</v>
+      </c>
+      <c r="N35" t="s">
+        <v>46</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>8000</v>
+      </c>
+      <c r="R35">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>1033</v>
+      </c>
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36">
+        <v>50</v>
+      </c>
+      <c r="F36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36">
+        <v>35000</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="I36" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" t="s">
+        <v>158</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>-1</v>
+      </c>
+      <c r="M36" t="s">
+        <v>43</v>
+      </c>
+      <c r="N36" t="s">
+        <v>42</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>4000</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>1034</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37">
+        <v>50</v>
+      </c>
+      <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37">
+        <v>35000</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+      <c r="I37" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" t="s">
+        <v>158</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>-1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>38</v>
+      </c>
+      <c r="N37" t="s">
+        <v>37</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>4000</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>1035</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s">
+        <v>34</v>
+      </c>
+      <c r="E38">
+        <v>50</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38">
+        <v>80000</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="0"/>
+        <v>8000</v>
+      </c>
+      <c r="I38" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" t="s">
+        <v>158</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>-1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>31</v>
+      </c>
+      <c r="N38" t="s">
+        <v>30</v>
+      </c>
+      <c r="O38">
+        <v>300</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C008D5-5B4B-40C3-9807-A1000646DEFB}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.296875" bestFit="1" customWidth="1"/>
@@ -542,252 +3384,266 @@
     <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="39.09765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.09765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+      <c r="P2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2000</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>150</v>
+      </c>
+      <c r="H3">
+        <f>G3/10</f>
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3">
-        <v>150</v>
-      </c>
-      <c r="I3">
-        <f>H3/10</f>
-        <v>15</v>
-      </c>
-      <c r="J3">
+      <c r="O3">
         <v>0.3</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2001</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>150</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H5" si="0">G4/10</f>
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4">
-        <v>150</v>
-      </c>
-      <c r="I4">
-        <f t="shared" ref="I4:I5" si="0">H4/10</f>
-        <v>15</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>0.3</v>
       </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4">
-        <v>10</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>2002</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="H5">
-        <v>250</v>
-      </c>
-      <c r="I5">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="J5">
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>10</v>
+      </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5">
         <v>0.4</v>
       </c>
-      <c r="K5">
+      <c r="P5">
         <v>0.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
-        <v>10</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -796,160 +3652,112 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82845201-2628-4823-B6D1-8A4642A35A02}">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="23" max="23" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="K1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L1" t="s">
         <v>5</v>
       </c>
       <c r="M1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="O1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" t="s">
-        <v>11</v>
-      </c>
-      <c r="S1" t="s">
-        <v>22</v>
-      </c>
-      <c r="T1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" t="s">
-        <v>10</v>
-      </c>
-      <c r="W1" t="s">
-        <v>8</v>
-      </c>
-      <c r="X1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" t="s">
-        <v>20</v>
-      </c>
-      <c r="T2" t="s">
-        <v>20</v>
-      </c>
-      <c r="U2" t="s">
-        <v>20</v>
-      </c>
-      <c r="V2" t="s">
-        <v>20</v>
-      </c>
-      <c r="W2" t="s">
-        <v>21</v>
-      </c>
-      <c r="X2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Server/Common/GameDatasheet/Original_Item.xlsx
+++ b/Server/Common/GameDatasheet/Original_Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE952D6-72E4-43CC-9C5B-DC9A877363A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546A3D44-E76B-4E40-B168-88C1D94B1806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-2700" windowWidth="13176" windowHeight="22656" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="195">
   <si>
     <t>class_requirement</t>
   </si>
@@ -231,9 +231,6 @@
     <t>"/Game/Assets/Icon/Sword_5.Sword_5"</t>
   </si>
   <si>
-    <t>"보석으로 장식된 화려한 검. 세게 휘두르면 나무도 자를 수 있다."</t>
-  </si>
-  <si>
     <t>"글라디우스"</t>
   </si>
   <si>
@@ -448,9 +445,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"날이 빠진 검. 맨손보다 나은 정도다."</t>
-  </si>
-  <si>
     <t>"FALSE"</t>
   </si>
   <si>
@@ -544,6 +538,128 @@
   </si>
   <si>
     <t>"FALSE"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"흔해 빠진 검. 보급형이라 적당히 쓰기 좋다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"금으로 장식된 화려한 검. 세게 휘두르면 나무도 자를 수 있다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Helmet.SK_Level0_Helmet</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Chest.SK_Level0_Chest</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Legs.SK_Level0_Legs</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Arms.SK_Level0_Arms</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Boots.SK_Level0_Boots</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Helmet.SK_Level10_Helmet</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Chest.SK_Level10_Chest</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Legs.SK_Level10_Legs</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Arms.SK_Level10_Arms</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Boots.SK_Level10_Boots</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Helmet.SK_Level20_Helmet</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Chest.SK_Level20_Chest</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Legs.SK_Level20_Legs</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Arms.SK_Level20_Arms</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Boots.SK_Level20_Boots</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Helmet.SK_Level30_Helmet</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Chest.SK_Level30_Chest</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Legs.SK_Level30_Legs</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Arms.SK_Level30_Arms</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Boots.SK_Level30_Boots</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Helmet.SK_Level40_Helmet</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Chest.SK_Level40_Chest</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Legs.SK_Level40_Legs</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Arms.SK_Level40_Arms</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Boots.SK_Level40_Boots</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Helmet.SK_Level50_Helmet</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Chest.SK_Level50_Chest</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Legs.SK_Level50_Legs</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Arms.SK_Level50_Arms</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Boots.SK_Level50_Boots</t>
+  </si>
+  <si>
+    <t>/Game/Assets/Swords/SM_Level50_Sword.SM_Level50_Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/Assets/Swords/SM_Level40_Sword.SM_Level40_Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/Assets/Swords/SM_Level30_Sword.SM_Level30_Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/Assets/Swords/SM_Level20_Sword.SM_Level20_Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/Assets/Swords/SM_Level10_Sword.SM_Level10_Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Game/Assets/Swords/SM_Level0_Sword.SM_Level0_Sword</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -961,7 +1077,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -976,25 +1092,25 @@
         <v>26</v>
       </c>
       <c r="O1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="S1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="U1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.4">
@@ -1067,13 +1183,13 @@
         <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1092,7 +1208,7 @@
         <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1101,10 +1217,10 @@
         <v>-1</v>
       </c>
       <c r="M3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1125,13 +1241,16 @@
       <c r="T3">
         <v>0</v>
       </c>
+      <c r="U3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
         <v>40</v>
@@ -1156,7 +1275,7 @@
         <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1165,10 +1284,10 @@
         <v>-1</v>
       </c>
       <c r="M4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1189,13 +1308,16 @@
       <c r="T4">
         <v>0</v>
       </c>
+      <c r="U4" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1002</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -1220,7 +1342,7 @@
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1229,10 +1351,10 @@
         <v>-1</v>
       </c>
       <c r="M5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1253,13 +1375,16 @@
       <c r="T5">
         <v>0</v>
       </c>
+      <c r="U5" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -1284,7 +1409,7 @@
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1293,10 +1418,10 @@
         <v>-1</v>
       </c>
       <c r="M6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1317,13 +1442,16 @@
       <c r="T6">
         <v>0</v>
       </c>
+      <c r="U6" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
@@ -1348,7 +1476,7 @@
         <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1357,10 +1485,10 @@
         <v>-1</v>
       </c>
       <c r="M7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1381,13 +1509,16 @@
       <c r="T7">
         <v>0</v>
       </c>
+      <c r="U7" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1005</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -1409,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1421,10 +1552,10 @@
         <v>-1</v>
       </c>
       <c r="M8" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="N8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1444,6 +1575,9 @@
       </c>
       <c r="T8">
         <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.4">
@@ -1451,7 +1585,7 @@
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
@@ -1476,7 +1610,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1485,10 +1619,10 @@
         <v>-1</v>
       </c>
       <c r="M9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1509,13 +1643,16 @@
       <c r="T9">
         <v>0</v>
       </c>
+      <c r="U9" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
@@ -1540,7 +1677,7 @@
         <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1549,10 +1686,10 @@
         <v>-1</v>
       </c>
       <c r="M10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1573,13 +1710,16 @@
       <c r="T10">
         <v>0</v>
       </c>
+      <c r="U10" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1008</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
         <v>40</v>
@@ -1604,7 +1744,7 @@
         <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1613,10 +1753,10 @@
         <v>-1</v>
       </c>
       <c r="M11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1637,13 +1777,16 @@
       <c r="T11">
         <v>0</v>
       </c>
+      <c r="U11" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
         <v>40</v>
@@ -1668,7 +1811,7 @@
         <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1677,10 +1820,10 @@
         <v>-1</v>
       </c>
       <c r="M12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -1701,13 +1844,16 @@
       <c r="T12">
         <v>0</v>
       </c>
+      <c r="U12" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
@@ -1732,7 +1878,7 @@
         <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1741,10 +1887,10 @@
         <v>-1</v>
       </c>
       <c r="M13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1765,13 +1911,16 @@
       <c r="T13">
         <v>0</v>
       </c>
+      <c r="U13" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>1011</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -1796,7 +1945,7 @@
         <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1805,10 +1954,10 @@
         <v>-1</v>
       </c>
       <c r="M14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O14">
         <v>35</v>
@@ -1828,6 +1977,9 @@
       </c>
       <c r="T14">
         <v>0</v>
+      </c>
+      <c r="U14" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.4">
@@ -1835,7 +1987,7 @@
         <v>1012</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
         <v>40</v>
@@ -1860,7 +2012,7 @@
         <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1869,10 +2021,10 @@
         <v>-1</v>
       </c>
       <c r="M15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1893,13 +2045,16 @@
       <c r="T15">
         <v>0</v>
       </c>
+      <c r="U15" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1013</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
         <v>40</v>
@@ -1924,7 +2079,7 @@
         <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1933,10 +2088,10 @@
         <v>-1</v>
       </c>
       <c r="M16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1957,13 +2112,16 @@
       <c r="T16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U16" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1014</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
         <v>40</v>
@@ -1988,7 +2146,7 @@
         <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -1997,10 +2155,10 @@
         <v>-1</v>
       </c>
       <c r="M17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -2021,13 +2179,16 @@
       <c r="T17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1015</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
@@ -2052,7 +2213,7 @@
         <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2061,10 +2222,10 @@
         <v>-1</v>
       </c>
       <c r="M18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -2085,13 +2246,16 @@
       <c r="T18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1016</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
@@ -2116,7 +2280,7 @@
         <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -2125,10 +2289,10 @@
         <v>-1</v>
       </c>
       <c r="M19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -2149,13 +2313,16 @@
       <c r="T19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>1017</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
@@ -2180,7 +2347,7 @@
         <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2189,10 +2356,10 @@
         <v>-1</v>
       </c>
       <c r="M20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O20">
         <v>80</v>
@@ -2213,13 +2380,16 @@
       <c r="T20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>1018</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
@@ -2244,7 +2414,7 @@
         <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2253,10 +2423,10 @@
         <v>-1</v>
       </c>
       <c r="M21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -2277,13 +2447,16 @@
       <c r="T21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1019</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
@@ -2308,7 +2481,7 @@
         <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2317,10 +2490,10 @@
         <v>-1</v>
       </c>
       <c r="M22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2341,13 +2514,16 @@
       <c r="T22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1020</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
@@ -2372,7 +2548,7 @@
         <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2381,10 +2557,10 @@
         <v>-1</v>
       </c>
       <c r="M23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -2405,13 +2581,16 @@
       <c r="T23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1021</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
         <v>40</v>
@@ -2436,7 +2615,7 @@
         <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2445,10 +2624,10 @@
         <v>-1</v>
       </c>
       <c r="M24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -2469,13 +2648,16 @@
       <c r="T24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>1022</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
@@ -2500,7 +2682,7 @@
         <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2509,10 +2691,10 @@
         <v>-1</v>
       </c>
       <c r="M25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -2533,13 +2715,16 @@
       <c r="T25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1023</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
         <v>35</v>
@@ -2564,7 +2749,7 @@
         <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2573,10 +2758,10 @@
         <v>-1</v>
       </c>
       <c r="M26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O26">
         <v>120</v>
@@ -2597,13 +2782,16 @@
       <c r="T26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>1024</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
         <v>40</v>
@@ -2628,7 +2816,7 @@
         <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2637,10 +2825,10 @@
         <v>-1</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -2661,13 +2849,16 @@
       <c r="T27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>1025</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
@@ -2692,7 +2883,7 @@
         <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2701,10 +2892,10 @@
         <v>-1</v>
       </c>
       <c r="M28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -2725,13 +2916,16 @@
       <c r="T28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U28" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>1026</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
@@ -2756,7 +2950,7 @@
         <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2765,10 +2959,10 @@
         <v>-1</v>
       </c>
       <c r="M29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -2789,13 +2983,16 @@
       <c r="T29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>1027</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
@@ -2820,7 +3017,7 @@
         <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -2829,10 +3026,10 @@
         <v>-1</v>
       </c>
       <c r="M30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -2853,13 +3050,16 @@
       <c r="T30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>1028</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>40</v>
@@ -2884,7 +3084,7 @@
         <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2893,10 +3093,10 @@
         <v>-1</v>
       </c>
       <c r="M31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -2917,13 +3117,16 @@
       <c r="T31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>1029</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
         <v>35</v>
@@ -2948,7 +3151,7 @@
         <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2957,7 +3160,7 @@
         <v>-1</v>
       </c>
       <c r="M32" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="N32" t="s">
         <v>58</v>
@@ -2981,8 +3184,11 @@
       <c r="T32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>1030</v>
       </c>
@@ -3012,7 +3218,7 @@
         <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -3045,8 +3251,11 @@
       <c r="T33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>1031</v>
       </c>
@@ -3076,7 +3285,7 @@
         <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3109,8 +3318,11 @@
       <c r="T34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U34" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>1032</v>
       </c>
@@ -3140,7 +3352,7 @@
         <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -3173,8 +3385,11 @@
       <c r="T35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>1033</v>
       </c>
@@ -3204,7 +3419,7 @@
         <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -3237,8 +3452,11 @@
       <c r="T36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>1034</v>
       </c>
@@ -3268,7 +3486,7 @@
         <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -3301,8 +3519,11 @@
       <c r="T37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U37" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>1035</v>
       </c>
@@ -3332,7 +3553,7 @@
         <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3364,6 +3585,9 @@
       </c>
       <c r="T38">
         <v>0</v>
+      </c>
+      <c r="U38" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3422,7 +3646,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -3689,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>

--- a/Server/Common/GameDatasheet/Original_Item.xlsx
+++ b/Server/Common/GameDatasheet/Original_Item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546A3D44-E76B-4E40-B168-88C1D94B1806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758B2E89-2246-40AB-8858-32CA32928D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-2700" windowWidth="13176" windowHeight="22656" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
   <sheets>
     <sheet name="전사 장비(1000~1999)" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="196">
   <si>
     <t>class_requirement</t>
   </si>
@@ -505,10 +505,6 @@
     <t>"초보자의 두건"</t>
   </si>
   <si>
-    <t>asset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mp_regenerate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -549,117 +545,119 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Helmet.SK_Level0_Helmet</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Chest.SK_Level0_Chest</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Legs.SK_Level0_Legs</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Arms.SK_Level0_Arms</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Boots.SK_Level0_Boots</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Helmet.SK_Level10_Helmet</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Chest.SK_Level10_Chest</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Legs.SK_Level10_Legs</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Arms.SK_Level10_Arms</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Boots.SK_Level10_Boots</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Helmet.SK_Level20_Helmet</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Chest.SK_Level20_Chest</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Legs.SK_Level20_Legs</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Arms.SK_Level20_Arms</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Boots.SK_Level20_Boots</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Helmet.SK_Level30_Helmet</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Chest.SK_Level30_Chest</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Legs.SK_Level30_Legs</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Arms.SK_Level30_Arms</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Boots.SK_Level30_Boots</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Helmet.SK_Level40_Helmet</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Chest.SK_Level40_Chest</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Legs.SK_Level40_Legs</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Arms.SK_Level40_Arms</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Boots.SK_Level40_Boots</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Helmet.SK_Level50_Helmet</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Chest.SK_Level50_Chest</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Legs.SK_Level50_Legs</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Arms.SK_Level50_Arms</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Boots.SK_Level50_Boots</t>
-  </si>
-  <si>
-    <t>/Game/Assets/Swords/SM_Level50_Sword.SM_Level50_Sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Assets/Swords/SM_Level40_Sword.SM_Level40_Sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Assets/Swords/SM_Level30_Sword.SM_Level30_Sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Assets/Swords/SM_Level20_Sword.SM_Level20_Sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Assets/Swords/SM_Level10_Sword.SM_Level10_Sword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Assets/Swords/SM_Level0_Sword.SM_Level0_Sword</t>
+    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Helmet.SK_Level0_Helmet"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Chest.SK_Level0_Chest"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Legs.SK_Level0_Legs"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Arms.SK_Level0_Arms"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor0R/SkeletalMeshes/SK_Level0_Boots.SK_Level0_Boots"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Swords/SM_Level0_Sword.SM_Level0_Sword"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Helmet.SK_Level10_Helmet"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Chest.SK_Level10_Chest"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Legs.SK_Level10_Legs"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Arms.SK_Level10_Arms"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor10R/SkeletalMeshes/SK_Level10_Boots.SK_Level10_Boots"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Swords/SM_Level10_Sword.SM_Level10_Sword"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Helmet.SK_Level20_Helmet"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Chest.SK_Level20_Chest"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Legs.SK_Level20_Legs"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Arms.SK_Level20_Arms"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor20R/SkeletalMeshes/SK_Level20_Boots.SK_Level20_Boots"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Swords/SM_Level20_Sword.SM_Level20_Sword"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Helmet.SK_Level30_Helmet"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Chest.SK_Level30_Chest"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Legs.SK_Level30_Legs"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Arms.SK_Level30_Arms"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor30R/SkeletalMeshes/SK_Level30_Boots.SK_Level30_Boots"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Swords/SM_Level30_Sword.SM_Level30_Sword"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Helmet.SK_Level40_Helmet"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Chest.SK_Level40_Chest"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Legs.SK_Level40_Legs"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Arms.SK_Level40_Arms"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor40R/SkeletalMeshes/SK_Level40_Boots.SK_Level40_Boots"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Swords/SM_Level40_Sword.SM_Level40_Sword"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Helmet.SK_Level50_Helmet"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Chest.SK_Level50_Chest"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Legs.SK_Level50_Legs"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Arms.SK_Level50_Arms"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Armors/Armor50R/SkeletalMeshes/SK_Level50_Boots.SK_Level50_Boots"</t>
+  </si>
+  <si>
+    <t>"/Game/Assets/Swords/SM_Level50_Sword.SM_Level50_Sword"</t>
+  </si>
+  <si>
+    <t>skeletal_mesh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>static_mesh</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1024,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E21C8A9-CEC2-4794-9B99-BAC1321823BA}">
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.296875" bestFit="1" customWidth="1"/>
@@ -1048,7 +1046,7 @@
     <col min="20" max="20" width="10.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1077,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -1092,28 +1090,31 @@
         <v>26</v>
       </c>
       <c r="O1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
+        <v>194</v>
+      </c>
+      <c r="V1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1177,8 +1178,11 @@
       <c r="U2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="V2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1000</v>
       </c>
@@ -1208,7 +1212,7 @@
         <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1242,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1001</v>
       </c>
@@ -1275,7 +1279,7 @@
         <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1309,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1002</v>
       </c>
@@ -1342,7 +1346,7 @@
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1376,10 +1380,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1003</v>
       </c>
@@ -1409,7 +1413,7 @@
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1443,10 +1447,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1004</v>
       </c>
@@ -1476,7 +1480,7 @@
         <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1510,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1005</v>
       </c>
@@ -1543,7 +1547,7 @@
         <v>130</v>
       </c>
       <c r="J8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -1552,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="M8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N8" t="s">
         <v>129</v>
@@ -1576,11 +1580,11 @@
       <c r="T8">
         <v>0</v>
       </c>
-      <c r="U8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="V8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1006</v>
       </c>
@@ -1610,7 +1614,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1647,7 +1651,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1007</v>
       </c>
@@ -1677,7 +1681,7 @@
         <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1714,7 +1718,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1008</v>
       </c>
@@ -1744,7 +1748,7 @@
         <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -1781,7 +1785,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1009</v>
       </c>
@@ -1811,7 +1815,7 @@
         <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -1848,7 +1852,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1010</v>
       </c>
@@ -1878,7 +1882,7 @@
         <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1915,7 +1919,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>1011</v>
       </c>
@@ -1945,7 +1949,7 @@
         <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1978,11 +1982,11 @@
       <c r="T14">
         <v>0</v>
       </c>
-      <c r="U14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="V14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>1012</v>
       </c>
@@ -2012,7 +2016,7 @@
         <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -2046,10 +2050,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1013</v>
       </c>
@@ -2079,7 +2083,7 @@
         <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2113,10 +2117,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1014</v>
       </c>
@@ -2146,7 +2150,7 @@
         <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -2180,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.4">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1015</v>
       </c>
@@ -2213,7 +2217,7 @@
         <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2247,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.4">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1016</v>
       </c>
@@ -2280,7 +2284,7 @@
         <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -2314,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>1017</v>
       </c>
@@ -2347,7 +2351,7 @@
         <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2380,11 +2384,11 @@
       <c r="T20">
         <v>0</v>
       </c>
-      <c r="U20" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="V20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>1018</v>
       </c>
@@ -2414,7 +2418,7 @@
         <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2448,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.4">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1019</v>
       </c>
@@ -2481,7 +2485,7 @@
         <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2515,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1020</v>
       </c>
@@ -2548,7 +2552,7 @@
         <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2582,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.4">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1021</v>
       </c>
@@ -2615,7 +2619,7 @@
         <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2649,10 +2653,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>1022</v>
       </c>
@@ -2682,7 +2686,7 @@
         <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2716,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1023</v>
       </c>
@@ -2749,7 +2753,7 @@
         <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2782,11 +2786,11 @@
       <c r="T26">
         <v>0</v>
       </c>
-      <c r="U26" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="V26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>1024</v>
       </c>
@@ -2816,7 +2820,7 @@
         <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -2850,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.4">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>1025</v>
       </c>
@@ -2883,7 +2887,7 @@
         <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -2917,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.4">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>1026</v>
       </c>
@@ -2950,7 +2954,7 @@
         <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -2984,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>1027</v>
       </c>
@@ -3017,7 +3021,7 @@
         <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -3051,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>1028</v>
       </c>
@@ -3084,7 +3088,7 @@
         <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -3118,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>1029</v>
       </c>
@@ -3151,7 +3155,7 @@
         <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -3160,7 +3164,7 @@
         <v>-1</v>
       </c>
       <c r="M32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N32" t="s">
         <v>58</v>
@@ -3184,11 +3188,11 @@
       <c r="T32">
         <v>0</v>
       </c>
-      <c r="U32" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="V32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>1030</v>
       </c>
@@ -3218,7 +3222,7 @@
         <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -3252,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>1031</v>
       </c>
@@ -3285,7 +3289,7 @@
         <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3319,10 +3323,10 @@
         <v>0</v>
       </c>
       <c r="U34" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>1032</v>
       </c>
@@ -3352,7 +3356,7 @@
         <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -3386,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>1033</v>
       </c>
@@ -3419,7 +3423,7 @@
         <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -3453,10 +3457,10 @@
         <v>0</v>
       </c>
       <c r="U36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>1034</v>
       </c>
@@ -3486,7 +3490,7 @@
         <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -3520,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="U37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.4">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>1035</v>
       </c>
@@ -3553,7 +3557,7 @@
         <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3586,8 +3590,8 @@
       <c r="T38">
         <v>0</v>
       </c>
-      <c r="U38" t="s">
-        <v>189</v>
+      <c r="V38" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3646,7 +3650,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -3913,7 +3917,7 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>

--- a/Server/Common/GameDatasheet/Original_Item.xlsx
+++ b/Server/Common/GameDatasheet/Original_Item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758B2E89-2246-40AB-8858-32CA32928D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF27072-6E1A-48AE-83D3-6DF6D51F559F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -1196,7 +1196,7 @@
         <v>146</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -1263,7 +1263,7 @@
         <v>52</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -1330,7 +1330,7 @@
         <v>48</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
@@ -1397,7 +1397,7 @@
         <v>44</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
@@ -1464,7 +1464,7 @@
         <v>39</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
         <v>33</v>
@@ -1531,17 +1531,16 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="s">
         <v>33</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>130</v>
